--- a/output/北塩原村_12重点施策_評価設計.xlsx
+++ b/output/北塩原村_12重点施策_評価設計.xlsx
@@ -122,7 +122,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -156,9 +156,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -526,7 +523,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -670,12 +667,12 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>原典が届いていない</t>
+          <t>原典を照合した</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>再レビューが引いている3資料（5742 高齢者サービスの手引き・5743 緊急連絡カード・6079 成年後見講座）は当セッションに届いていない。このため、事業名・対象要件は計画本文に書かず照会に回した。村民向け路線バスICカード事業と移動支援の対象事業所の把握不足、会津権利擁護・成年後見センターは当方の原典で裏づけが取れる</t>
+          <t>再レビューが引いている3資料は令和8年10月10日に受領し、source/村資料_高齢者施策_20261010 に格納した。本書の記述は原典で照合してある。手引きの福祉サービスはいずれも対象を「高齢者世帯等」「65歳以上」「概ね60歳以上」としており、障がいのある方が「等」に含まれるかは手引きから読み取れない。ただし成年後見制度の助成は「障がいや認知症などにより」と障がいのある方を明示している</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -687,32 +684,49 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>正本への反映</t>
+          <t>原典から新たに見つけたこと</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>修正案10件。うち枠組みとして今すぐ追記できるもの7件、照会の回答後とするもの6件</t>
+          <t>村内の介護保険の事業所は7カ所ある（居宅介護支援、介護予防支援、訪問介護、通所介護2カ所、認知症対応型共同生活介護2カ所）。このうち訪問介護1カ所と通所介護2カ所は共生型サービスの指定を受けられるため、働きかけの相手が具体的に分かった。障がい福祉の事業所が村内に3カ所しかない本村では、確保のための方策の中心になりうる</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>09シート</t>
+          <t>09シート W-11</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
+          <t>正本への反映</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>修正案12件。うち枠組みとして今すぐ追記できるもの11件、照会の回答後とするもの4件</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>09シート</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
           <t>村への照会</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>6件（M-49〜M-54）。M-50（高齢者福祉施策の対象要件と手引きの提供）が最も効く。1枚で65歳移行・住まい・冬季支援・移動の4つに答えが出る</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>08シート</t>
         </is>
@@ -733,7 +747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -813,12 +827,12 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>追記できる（制度の考え方として書く。個別の事業名は照会M-50の回答後）</t>
+          <t>追記できる（制度の考え方として書く。個別の事業の対象要件は照会M-50の回答後）</t>
         </is>
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>一部原典あり</t>
+          <t>原典あり（高齢者サービスの手引き）</t>
         </is>
       </c>
     </row>
@@ -840,7 +854,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>再レビュー2。アンケート調査.pdf（資料3）、意見・提案No.5・6・12</t>
+          <t>再レビュー2。アンケート調査.pdf（資料3）、意見・提案No.5・6・12、高齢者サービスの手引き</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -848,9 +862,9 @@
           <t>追記できる</t>
         </is>
       </c>
-      <c r="F7" s="10" t="inlineStr">
-        <is>
-          <t>一部原典あり</t>
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>原典あり</t>
         </is>
       </c>
     </row>
@@ -894,27 +908,27 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>第4章2（4）／第5章1（2）</t>
+          <t>第5章2（11）災害時の備え（W-8の後）</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>医療的ケア児者・重度障がい者について、救急時に持病・常用薬・かかりつけ医が伝わる仕組みとの接続を書く。「配布する」と確定で書かず、既存の仕組みの活用状況を確認し必要に応じ対象拡大・周知を図ると書く</t>
+          <t>救急時に持病、常用薬及びかかりつけ医が伝わる様式が村にあることと、障がいの特性・意思疎通の方法・医療的ケアの内容を書き加えられるようにすることを書く。「配布する」と確定で書かず、活用の状況を確認し必要に応じ対象の拡大と周知を図ると書く</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>再レビュー6。緊急連絡カード（原典未入手）</t>
+          <t>再レビュー6。緊急連絡カードの様式</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>照会M-52の回答後</t>
-        </is>
-      </c>
-      <c r="F9" s="13" t="inlineStr">
-        <is>
-          <t>原典未入手</t>
+          <t>追記できる</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t>原典あり</t>
         </is>
       </c>
     </row>
@@ -944,9 +958,9 @@
           <t>照会M-53の回答後（村に職親委託の実績があるかを確認）</t>
         </is>
       </c>
-      <c r="F10" s="13" t="inlineStr">
-        <is>
-          <t>原典未入手</t>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>原典なし（3資料に記載がない）</t>
         </is>
       </c>
     </row>
@@ -978,7 +992,7 @@
       </c>
       <c r="F11" s="10" t="inlineStr">
         <is>
-          <t>一部原典あり</t>
+          <t>原典あり（正本 第6章）</t>
         </is>
       </c>
     </row>
@@ -995,76 +1009,76 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>親が亡くなった後の住まいの選択肢として、共同生活援助だけでなく高齢者向けの住まいも個別に比べる旨を書く。「生活支援ハウスを利用できる」とは書かない（対象要件が未確認であり、障がいのある方が当然利用できるとは言えない）</t>
+          <t>親が亡くなった後の住まいの選択肢として、共同生活援助だけでなく高齢者向けの住まいも個別に比べる旨を書く。村の生活支援ハウス（概ね60歳以上で自宅での独立した生活に不安のある方向け。管理人が常駐）を名指しで挙げるが、「障がいのある方が利用できる」とは書かず、対象となるかを事業ごとに確認すると書く</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>再レビュー5</t>
+          <t>再レビュー5。高齢者サービスの手引き</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>照会M-50の回答後</t>
-        </is>
-      </c>
-      <c r="F12" s="13" t="inlineStr">
-        <is>
-          <t>原典未入手</t>
+          <t>追記できる</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>原典あり</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>W-8</t>
+          <t>W-11</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>第5章2（11）災害時の備え</t>
+          <t>第5章2（4）広域連携によるサービス提供体制の確保</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>平時・急病時・介護者不在時・災害時の4場面に分けて、それぞれの仕組みと障がい分野での状態を書く</t>
+          <t>村内の介護保険の事業所7カ所（居宅介護支援、介護予防支援、訪問介護、通所介護2カ所、認知症対応型共同生活介護2カ所）を示し、うち訪問介護1カ所と通所介護2カ所は共生型サービスの指定により障がい福祉サービスを提供できることから、働きかけの相手が具体的に分かることを書く</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>再レビュー7</t>
+          <t>高齢者サービスの手引きのサービス事業者一覧。障害者総合支援法第41条の2（共生型障害福祉サービス）</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>枠組みは追記できる（個別の仕組み名は照会の回答後）</t>
-        </is>
-      </c>
-      <c r="F13" s="10" t="inlineStr">
-        <is>
-          <t>一部原典あり</t>
+          <t>追記できる</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="inlineStr">
+        <is>
+          <t>原典あり</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>W-9</t>
+          <t>W-12</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>第3章3 基本施策の目標値（評価の様式）</t>
+          <t>第6章1（3）成年後見制度利用支援事業の利用状況</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>評価を「実施／未実施」の2択にせず、6区分（①障害福祉で実施／②他制度で対応／③圏域で対応／④ニーズなし／⑤ニーズあり・供給不足／⑥把握不足）で書く旨を注記する</t>
+          <t>村の成年後見制度の利用支援が「障がいや認知症などにより」自身で決めることに不安のある方を対象としており、申立てに要する経費及び後見人等の報酬を助成するものであること、令和8年度に会津圏域11市町村と中核機関の共催で住民向けの成年後見講座を開催していることを書く</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>再レビュー9</t>
+          <t>高齢者サービスの手引き・令和8年度住民向け成年後見講座</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -1072,39 +1086,103 @@
           <t>追記できる</t>
         </is>
       </c>
-      <c r="F14" s="9" t="inlineStr">
-        <is>
-          <t>原典あり（村の評価シートの様式）</t>
+      <c r="F14" s="12" t="inlineStr">
+        <is>
+          <t>原典あり</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
+          <t>W-8</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>第5章2（11）災害時の備え</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>平時・急病時・介護者不在時・災害時の4場面に分けて、それぞれの仕組みと障がい分野での状態を書く</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>再レビュー7。緊急通報システム事業・緊急連絡カード</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>枠組みは追記できる（配布対象と活用状況は照会M-52の回答後）</t>
+        </is>
+      </c>
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>原典あり（高齢者サービスの手引き・緊急連絡カード）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>W-9</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>第3章3 基本施策の目標値（評価の様式）</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>評価を「実施／未実施」の2択にせず、6区分（①障害福祉で実施／②他制度で対応／③圏域で対応／④ニーズなし／⑤ニーズあり・供給不足／⑥把握不足）で書く旨を注記する</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>再レビュー9</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>追記できる</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>原典あり（村の評価シートの様式）</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
           <t>W-10</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>第1章6 計画の推進体制</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>年次の点検評価に用いる様式として7列（実績／ニーズ／障害福祉での供給／他制度による代替・補完／圏域利用／未充足／令和9〜11年度の対応）を定める旨を書く</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>再レビューの結論</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>追記できる</t>
         </is>
       </c>
-      <c r="F15" s="10" t="inlineStr">
+      <c r="F17" s="10" t="inlineStr">
         <is>
           <t>原典あり（法第88条の2）</t>
         </is>
@@ -1125,7 +1203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1411,6 +1489,134 @@
         <is>
           <t>年次の点検評価は、事業ごとに次の七つの項目により行います。本村では、村内に事業所がないサービスや、一般の施策により外出の手段が確保されているものがあり、実績の多少だけでは評価できないためです。
 ［表］項目 ／ 書くこと（7行）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>W-4</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>表の後</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>第5章2（11）災害時の備え（W-8の4場面の表の後）</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>本村では、本人の身に何か起きたときの備えが場面ごとに分かれています。どの場面にどの仕組みが働くのかを整理したうえで、障が…</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>再レビュー6。村の緊急連絡カードの様式</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>このうち急病時については、村に、住所、氏名、生年月日、持病と常用している薬、かかりつけ医及び緊急連絡先を記入し、本人の同意のうえで電話機や冷蔵庫の近くに備え付けて救急隊に伝える様式があります。この様式には障がいの特性、意思疎通の方法及び医療的ケアの内容を書く欄がないため、備考の欄にこれらを書き加えられるようにすることを検討します。医療的ケアが必要な方、重度の障がいのある方及びひとり暮らしの方について、この様式がどの程度使われているかを確かめたうえで、必要に応じて対象の拡大と周知を図ります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>W-7</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>第5章1（3）居住系サービス（移植11の後）</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>なお、国の基本指針は、生活介護、就労継続支援Ｂ型及び施設入所支援の必要な量の見込みについて、継続入所者（計画期間の開始前…</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>再レビュー5。令和8年度 北塩原村高齢者サービスの手引き</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>親が亡くなった後の住まいを考えるときには、共同生活援助だけを前提とせず、本人の年齢と必要な支援に応じて選択肢を比べます。本村には、概ね60歳以上で自宅での独立した生活に不安のある方を対象とし、管理人が常駐する一人暮らし高齢者向けの住まい（生活支援ハウス）があります。知的障がい又は精神障がいのある方が60歳代に入り、親が亡くなって独居が難しくなる場合には、共同生活援助とこうした高齢者向けの住まいのどちらが本人に合うかを、介護保険の利用の可否とあわせて個別に検討します。なお、高齢者向けの事業は対象を高齢者世帯等としており、障がいのある方が対象となるかは事業ごとに確認します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>W-11</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>第5章2（4）広域連携によるサービス提供体制の確保</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>本村は人口規模が小さく、村内に障がい福祉サービス事業所が少ないことから、多くのサービスを近隣市町村の事業所に依存していま…</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>令和8年度 北塩原村高齢者サービスの手引きのサービス事業者一覧。障害者総合支援法第41条の2（共生型障害福祉サービス）</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>本村には障がい福祉サービスの事業所が３カ所しかありませんが、介護保険の事業所は７カ所あります（居宅介護支援、介護予防支援、訪問介護、通所介護２カ所、認知症対応型共同生活介護２カ所）。このうち訪問介護及び通所介護の事業所は、共生型サービスの指定を受けることにより、介護保険の指定を受けたまま障がい福祉サービスを提供できます。共生型サービスの対象となるのは訪問介護、通所介護及び短期入所生活介護であり、村内では訪問介護１カ所と通所介護２カ所がこれに当たります。本計画期間においては、この３カ所に対して、村から共生型サービス又は基準該当サービスの指定を受けることを働きかけます。村内で居宅介護又は生活介護を受けられるようになれば、冬季の通所と送迎の制約が小さくなります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>W-12</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>第6章1（3）成年後見制度利用支援事業の利用状況</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>このような状況の中、本村における高齢化の進展や精神障がい者、知的障がい者の人数の推移から、本制度の必要性はますます高まっ…</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>令和8年度 北塩原村高齢者サービスの手引き・令和8年度住民向け成年後見講座</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>本村の成年後見制度の利用支援は、障がいや認知症などにより自身で決めることに不安のある方を対象とし、申立てに要する経費及び後見人等の報酬を助成するものです（一定の要件があります）。高齢の方だけでなく、障がいのある方も対象です。また令和８年度には、会津圏域の11市町村と会津権利擁護・成年後見センターの共催により、住民向けの成年後見講座を開催しています。本村はその主催者の一員であり、障がいのある方とその家族にも参加を呼びかけます。</t>
         </is>
       </c>
     </row>
@@ -1441,14 +1647,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>再レビューが引いている3資料の扱い</t>
+          <t>再レビューが引いている3資料（令和8年10月10日に受領）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>3資料は当セッションに届いていない（添付が配信されなかった）。このため事業名・対象要件は計画本文に書かず、照会に回している。再送いただければ原典で照合する。</t>
+          <t>3資料は source/村資料_高齢者施策_20261010 に格納した。本書の記述は原典で照合してある（手引き16語・講座5語を自己点検で毎回照合）。</t>
         </is>
       </c>
     </row>
@@ -1465,12 +1671,12 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>再レビューが引いている内容</t>
+          <t>原典で確かめた内容</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>当方の状態</t>
+          <t>読み取り</t>
         </is>
       </c>
     </row>
@@ -1482,17 +1688,17 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>令和8年度 北塩原村高齢者サービスの手引き</t>
+          <t>令和8年度 北塩原村高齢者サービスの手引き（3頁・令和8年4月発行）</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>生活支援ハウス、緊急通報システム（お元気コール）、高齢者世帯等除雪サービス事業、寝具洗濯、訪問理美容、弁当配達（配食）、家族介護継続支援、介護用品助成、成年後見申立費用及び後見人等報酬の助成、村民向け路線バスICカード、無料コミュニティバス</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>村民向け路線バスICカード事業のみ、アンケート調査.pdf（資料3）で裏づけが取れる。ほかの事業の名称・対象要件・実績は当方未確認</t>
+          <t>相談窓口6件、生きがい・活動3件、教室・イベント4件、健康6件、お祝い1件、福祉サービス13件、村内のサービス事業者一覧7事業所</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>原典で確認。福祉サービスの対象はいずれも「高齢者世帯等」「65歳以上」「概ね60歳以上」「在宅介護高齢者等」であり、障がいのある方（65歳未満）が「等」に含まれるかは手引きからは読み取れない。ただし成年後見制度の助成は「障がいや認知症などにより」と障がいのある方を明示している</t>
         </is>
       </c>
     </row>
@@ -1504,17 +1710,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>緊急連絡カード</t>
+          <t>緊急連絡カード（1頁。画像のみの様式）</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>本人情報・生年月日・持病・常用薬・かかりつけ医・緊急連絡先・備考を記入し、電話機や冷蔵庫付近に備えて救急隊が活用する仕組み</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>様式そのものを当方は見ていない。障がい者・医療的ケア児者への配布・活用状況は再レビューも「資料から確認できない」としている</t>
+          <t>2人分の様式。住所・固定電話、氏名、性別、血液型、携帯電話、生年月日、持病・お薬、かかりつけ医、緊急連絡先2件、備考。「緊急時にこのカードの情報を支援者が活用することに同意します」という本人の同意欄。電話機や冷蔵庫の近くに備え付ける</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>原典で確認。2人分の様式であり高齢者の夫婦世帯を想定した作り。障がいの特性、意思疎通の方法、医療的ケアの内容を書く欄はなく、備考欄に頼ることになる。発行者名・配布対象・配布実績はカードに記載がないため照会M-52は引き続き要る</t>
         </is>
       </c>
     </row>
@@ -1526,24 +1732,24 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>会津権利擁護・成年後見センターの住民向け成年後見講座</t>
+          <t>令和8年度住民向け成年後見講座（2頁）</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>令和8年度に北塩原村を含む会津地域11市町村とセンターが共同で住民向け成年後見講座を開催。村の窓口が明示されている</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>センターの設置（令和4年7月・11市町村）と市民後見人養成事業（令和6年度追加）は正本 第6章2にあり裏づけが取れる。令和8年度の講座の開催と村の窓口の表示は当方未確認</t>
+          <t>創作劇とトークセッションの2部。10月23日（金）会津若松市文化センター200名、10月24日（土）金山町民体育館100名。入場無料。申込期限10月16日（金）。主催は会津若松市・北塩原村・磐梯町・猪苗代町・会津坂下町・湯川村・柳津町・三島町・金山町・昭和村・会津美里町の11市町村と会津権利擁護・成年後見センター。村の担当は保健福祉課</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>原典で確認。本村は主催者の一員である。内容はおひとり様・終活・後見契約が主題で高齢者向けの作りだが、権利擁護の普及啓発の実績として第6章に書ける。申込期限が令和8年10月16日であり、障がいのある方とその家族への周知は今からでも間に合う</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>※ 当方の原典で裏づけが取れているもの：村民向け路線バスICカード事業（アンケート調査.pdf 資料3）、移動支援の対象事業所の把握不足（意見・提案.pdf No.5）、会津権利擁護・成年後見センターと成年後見制度利用支援事業の利用状況（正本 第6章）。</t>
+          <t>※ 別の原典で裏づけが取れているもの：村民向け路線バスICカード事業の創設年度（アンケート調査.pdf 資料3）、移動支援の対象事業所の把握不足（意見・提案.pdf No.5）、会津権利擁護・成年後見センターの設置と成年後見制度利用支援事業の利用状況（正本 第6章）。なお職親委託制度は3資料に記載がなく、照会M-53のままである。</t>
         </is>
       </c>
     </row>
@@ -2012,12 +2218,12 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>介護保険に相当するサービスの有無による4区分と、適用除外・第2号被保険者・共生型・新高額障害福祉サービス等給付費は正本に入れた。移行先に村の高齢者福祉施策・村単独事業を加える整理は未反映（修正案W-1）</t>
-        </is>
-      </c>
-      <c r="H17" s="8" t="inlineStr">
-        <is>
-          <t>再レビューによる（手引きの事業名は原典未入手）</t>
+          <t>介護保険に相当するサービスの有無による4区分と、適用除外・第2号被保険者・共生型・新高額障害福祉サービス等給付費は正本に入れた。移行先に村の高齢者福祉施策・村単独事業を加える整理はW-1として正本に入れた</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>原典あり（高齢者サービスの手引き）</t>
         </is>
       </c>
     </row>
@@ -2054,12 +2260,12 @@
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>移動支援の見込量は0人。村の回答は「対象事業所の把握ができていなかった」であり、ニーズがないことの確認ではない。7パターンの切り分け（05シート）は未反映（修正案W-2）</t>
-        </is>
-      </c>
-      <c r="H18" s="8" t="inlineStr">
-        <is>
-          <t>一部原典あり（ICカード事業と村の回答）／コミュニティバス・除雪事業は原典未入手</t>
+          <t>移動支援の見込量は0人。村の回答は「対象事業所の把握ができていなかった」であり、ニーズがないことの確認ではない。7パターンの切り分け（05シート）はW-2として正本に入れた</t>
+        </is>
+      </c>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>原典あり（ICカード事業・コミュニティバス・除雪事業とも高齢者サービスの手引きで確認）</t>
         </is>
       </c>
     </row>
@@ -2138,12 +2344,12 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>医療的ケア児等コーディネーターと協議の場は正本にある。救急医療情報（持病・常用薬・かかりつけ医）との接続は未反映（修正案W-4）。村資料にある「医療的ケアサポート会議」との関係は照会M-41</t>
-        </is>
-      </c>
-      <c r="H20" s="8" t="inlineStr">
-        <is>
-          <t>再レビューによる（緊急連絡カードは原典未入手）</t>
+          <t>医療的ケア児等コーディネーターと協議の場は正本にある。救急医療情報（持病・常用薬・かかりつけ医）との接続はW-4として正本に入れた。村資料にある「医療的ケアサポート会議」との関係は照会M-41</t>
+        </is>
+      </c>
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>原典あり（緊急連絡カードの様式を確認）</t>
         </is>
       </c>
     </row>
@@ -2222,12 +2428,12 @@
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>成年後見制度利用支援事業の利用状況（令和5年度1人→令和7年度3人）と会津権利擁護・成年後見センター（令和4年7月・11市町村・市民後見人養成事業）は正本にある。住まい・緊急時・家族の高齢化との一体評価と名称変更は未反映（修正案W-6・W-7）</t>
-        </is>
-      </c>
-      <c r="H22" s="8" t="inlineStr">
-        <is>
-          <t>一部原典あり（正本 第6章）／生活支援ハウス・申立費用助成の対象要件は原典未入手</t>
+          <t>成年後見制度利用支援事業の利用状況（令和5年度1人→令和7年度3人）と会津権利擁護・成年後見センター（令和4年7月・11市町村・市民後見人養成事業）は正本にある。住まい・緊急時・家族の高齢化との一体評価はW-6、高齢者向けの住まいとの比較はW-7、成年後見の助成と講座の実績はW-12として正本に入れた</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>原典あり（高齢者サービスの手引き・成年後見講座）</t>
         </is>
       </c>
     </row>
@@ -2306,12 +2512,12 @@
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>個別避難計画は13カ所、業務継続計画は2カ所で言及がある。4場面（平時・急病時・介護者不在時・災害時）での再構成は未反映（修正案W-8）。緊急通報・緊急連絡カードは正本に0件</t>
-        </is>
-      </c>
-      <c r="H24" s="8" t="inlineStr">
-        <is>
-          <t>再レビューによる（緊急通報・緊急連絡カードは原典未入手）</t>
+          <t>個別避難計画は13カ所、業務継続計画は2カ所で言及がある。4場面（平時・急病時・介護者不在時・災害時）での再構成はW-8として正本に入れた</t>
+        </is>
+      </c>
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>原典あり（緊急通報システム事業・緊急連絡カード）</t>
         </is>
       </c>
     </row>
@@ -2687,12 +2893,12 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>障がいのみを理由とする世帯が対象になるかを確認していない（照会M-49）</t>
-        </is>
-      </c>
-      <c r="E19" s="8" t="inlineStr">
-        <is>
-          <t>再レビューによる（原典未入手）</t>
+          <t>事業は「除雪が困難な高齢者世帯等」を対象とし、非課税世帯に居宅の除雪経費の一部を助成するもの。「等」に障がいのみを理由とする世帯が含まれるかを確認していない（照会M-49）</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>原典あり（高齢者サービスの手引き）／対象の範囲は未確認</t>
         </is>
       </c>
     </row>
@@ -3056,12 +3262,12 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>再レビューの修正点。65歳以降の生活を支えるのは介護保険給付だけではないため、移行先を介護保険に限ると評価が実態と合わない</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>再レビューによる（手引きは原典未入手。照会M-50）</t>
+          <t>再レビューの修正点。65歳以降の生活を支えるのは介護保険給付だけではないため、移行先を介護保険に限ると評価が実態と合わない。手引きには福祉サービス13件が載っており、いずれも対象を高齢者世帯等としている</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>原典あり（高齢者サービスの手引き）／障がいのある方が対象となるかは照会M-50</t>
         </is>
       </c>
     </row>
@@ -3225,7 +3431,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>ICカード事業は令和6年度創設。喜多方－裏磐梯・猪苗代－裏磐梯の路線バスを無料化（現物給付）。路線バス区域外の無料コミュニティバスは原典未入手</t>
+          <t>ICカード事業は令和6年度創設。喜多方⇔裏磐梯・猪苗代⇔裏磐梯の路線バスを無料化（現物給付）。路線バス運行区域以外でも無料のコミュニティバスが運行している（高齢者サービスの手引きで確認）</t>
         </is>
       </c>
     </row>
@@ -3727,12 +3933,12 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>緊急通報システム（固定電話型。65歳以上のひとり暮らし高齢者世帯等）、お元気コール</t>
+          <t>緊急通報システム事業（65歳以上のひとり暮らし高齢者世帯等で固定電話をお持ちの方。設置費・使用料は無料（非課税者等）、通信料は本人負担。定期的に「お元気コール」を実施し安否確認）</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>障がいのある方が対象になるかを確認していない。正本に0件</t>
+          <t>対象が65歳以上のひとり暮らし高齢者世帯等であり、障がいのある方（65歳未満）が「等」に含まれるかは手引きから読み取れない。正本に0件</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -3754,12 +3960,12 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>緊急連絡カード（本人情報・生年月日・持病・常用薬・かかりつけ医・緊急連絡先・備考。電話機や冷蔵庫付近に備え救急隊が活用）</t>
+          <t>緊急連絡カード（2人分の様式。住所・固定電話、氏名、性別、血液型、携帯電話、生年月日、持病・お薬、かかりつけ医、緊急連絡先2件、備考。本人の同意欄があり、電話機や冷蔵庫の近くに備え付ける）</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>障がい者・医療的ケア児者・独居の障がいのある方への配布・活用状況が分からない。正本に0件</t>
+          <t>障がいの特性、意思疎通の方法、医療的ケアの内容を書く欄がなく、備考欄に頼ることになる。配布対象・配布実績はカードに記載がない。正本に0件</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -3896,12 +4102,12 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>高齢者世帯等除雪サービス事業の対象要件</t>
+          <t>高齢者世帯等除雪サービス事業の「等」の範囲</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>①障がいのみを理由とする世帯が対象となるか②障がいのある方が属する世帯の利用実績（令和6・7年度）③対象要件（年齢・世帯構成・所得・除雪困難の判定）</t>
+          <t>手引きでは「除雪が困難な高齢者世帯等」を対象とし、非課税世帯に居宅の除雪経費の一部を助成するとされている。①「等」に障がいのみを理由とする世帯が含まれるか②障がいのある方が属する世帯の利用実績（令和6・7年度）③助成の上限額と申請の方法</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -3923,17 +4129,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>高齢者福祉施策・村単独事業の対象要件と利用実績</t>
+          <t>高齢者福祉施策の「高齢者世帯等」に障がいのある方が入るか</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>令和8年度 北塩原村高齢者サービスの手引きに載る事業について、①事業名の一覧②それぞれの対象要件③障がいのある方（65歳未満を含む）が対象になるか④障がいのある方の利用実績。とくに生活支援ハウス、緊急通報システム、寝具洗濯、訪問理美容、配食、家族介護継続支援、介護用品助成、無料コミュニティバス</t>
+          <t>手引きは受領した。福祉サービス13件の対象はいずれも「高齢者世帯等」「65歳以上」「概ね60歳以上」「在宅介護高齢者等」である。①このうち障がいのある方（65歳未満を含む）が対象となる事業はどれか②生活支援ハウスの入居要件と空き状況③緊急通報システム事業の「等」の範囲④障がいのある方の利用実績（令和6・7年度）</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>65歳到達者の移行先を介護保険給付に限ると評価が実態と合わない。住まいの選択肢を比べるためにも対象要件が要る。手引きそのものを1部いただきたい（当方未入手）</t>
+          <t>65歳到達者の移行先を介護保険給付に限ると評価が実態と合わない。住まいの選択肢を比べるためにも「等」の範囲が要る。成年後見制度の助成だけは「障がいや認知症などにより」と障がいのある方が明示されている</t>
         </is>
       </c>
       <c r="E7" s="10" t="inlineStr">
@@ -3977,17 +4183,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>緊急連絡カード・緊急通報システムの障がい分野での活用</t>
+          <t>緊急連絡カードの配布対象と障がい分野での活用</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>①緊急連絡カードの配布対象と配布実績②障がい者・医療的ケア児者・独居の障がいのある方への配布・活用状況③緊急通報システムの対象要件と障がいのある方の設置実績④救急隊との情報共有の仕組み</t>
+          <t>様式は受領した（2人分。持病・お薬、かかりつけ医、緊急連絡先、備考、本人の同意欄）。①配布の対象と実績②実施している課と事業名③障がいのある方・医療的ケアが必要な方・ひとり暮らしの方への配布と活用の状況④消防（救急隊）との情報共有の取決めの有無⑤備考欄に障がいの特性や意思疎通の方法を書いている例があるか</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>計画に「障がい者へ配布する」と確定で書く前に、既存の仕組みの対象と活用状況を確かめる必要がある</t>
+          <t>様式には障がいの特性・意思疎通の方法・医療的ケアの内容を書く欄がないため、備考欄の使い方が要になる。計画に「障がい者へ配布する」と確定で書く前に活用の状況を確かめる必要がある</t>
         </is>
       </c>
       <c r="E9" s="10" t="inlineStr">

--- a/output/北塩原村_12重点施策_評価設計.xlsx
+++ b/output/北塩原村_12重点施策_評価設計.xlsx
@@ -15,10 +15,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_No6 移動支援0人の切り分け" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_No10 地域生活継続・親亡き後・権利擁護" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_緊急時の4場面" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_村への照会" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_正本への反映" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09b_正本に入れる文章" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_原典の状態" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08b_除雪支援の整理" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_村への照会" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_正本への反映" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09b_正本に入れる文章" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_原典の状態" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -667,66 +668,83 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>原典を照合した</t>
+          <t>除雪支援は新設から考えない</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>再レビューが引いている3資料は令和8年10月10日に受領し、source/村資料_高齢者施策_20261010 に格納した。本書の記述は原典で照合してある。手引きの福祉サービスはいずれも対象を「高齢者世帯等」「65歳以上」「概ね60歳以上」としており、障がいのある方が「等」に含まれるかは手引きから読み取れない。ただし成年後見制度の助成は「障がいや認知症などにより」と障がいのある方を明示している</t>
+          <t>村には「高齢者世帯等除雪サービス事業」があり、除雪が困難な高齢者世帯等に居宅の除雪経費の一部を助成している。障がい者向けの除雪事業を新設すると直ちに書くのではなく、①既存事業で障がい者世帯も対象となるか②一部のみ対象となるか③対象外で未充足のニーズがあるかの3段階で整理する。評価は「②他の制度で対応の可能性あり＋⑥把握不足」とし、対象要件と実績が分かった段階で判定し直す</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>08bシート。照会M-49・M-55〜M-58</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>原典から新たに見つけたこと</t>
+          <t>原典を照合した</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>村内の介護保険の事業所は7カ所ある（居宅介護支援、介護予防支援、訪問介護、通所介護2カ所、認知症対応型共同生活介護2カ所）。このうち訪問介護1カ所と通所介護2カ所は共生型サービスの指定を受けられるため、働きかけの相手が具体的に分かった。障がい福祉の事業所が村内に3カ所しかない本村では、確保のための方策の中心になりうる</t>
+          <t>再レビューが引いている3資料は令和8年10月10日に受領し、source/村資料_高齢者施策_20261010 に格納した。本書の記述は原典で照合してある。手引きの福祉サービスはいずれも対象を「高齢者世帯等」「65歳以上」「概ね60歳以上」としており、障がいのある方が「等」に含まれるかは手引きから読み取れない。ただし成年後見制度の助成は「障がいや認知症などにより」と障がいのある方を明示している</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>09シート W-11</t>
+          <t>10シート</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>正本への反映</t>
+          <t>原典から新たに見つけたこと</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>修正案12件。うち枠組みとして今すぐ追記できるもの11件、照会の回答後とするもの4件</t>
+          <t>村内の介護保険の事業所は7カ所ある（居宅介護支援、介護予防支援、訪問介護、通所介護2カ所、認知症対応型共同生活介護2カ所）。このうち訪問介護1カ所と通所介護2カ所は共生型サービスの指定を受けられるため、働きかけの相手が具体的に分かった。障がい福祉の事業所が村内に3カ所しかない本村では、確保のための方策の中心になりうる</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>09シート</t>
+          <t>09シート W-11</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
+          <t>正本への反映</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>修正案13件。うち枠組みとして今すぐ追記できるもの12件、照会の回答後とするもの4件</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>09シート</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
           <t>村への照会</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>6件（M-49〜M-54）。M-50（高齢者福祉施策の対象要件と手引きの提供）が最も効く。1枚で65歳移行・住まい・冬季支援・移動の4つに答えが出る</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>10件（M-49〜M-58）。M-50（高齢者福祉施策の対象要件と手引きの提供）が最も効く。1枚で65歳移行・住まい・冬季支援・移動の4つに答えが出る</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>08シート</t>
         </is>
@@ -747,7 +765,343 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:E15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="64" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>この再レビューで生じた村への照会（M-49〜M-58）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>既存の照会はM-48まで。M-50（高齢者福祉施策の対象要件と手引きの提供）は、1枚で65歳移行・住まい・冬季支援・移動の4つに答えが出る。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>番号</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>事項</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>聞きたいこと</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>なぜ要るか</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>期限の目安</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>M-49</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>高齢者世帯等除雪サービス事業の「等」の範囲</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>手引きでは「除雪が困難な高齢者世帯等」を対象とし、非課税世帯に居宅の除雪経費の一部を助成するとされている。①「等」に障がいのみを理由とする世帯が含まれるか②障がいのある方が属する世帯の利用実績（令和6・7年度）③助成の上限額と申請の方法</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>対象であれば既存事業の活用として書き、対象外でニーズがあれば対象拡大又は障害福祉での補完を検討する。障がい者向け除雪事業を新設すると直ちに書くのは順序が逆になる</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>令和8年10月20日</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>M-50</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>高齢者福祉施策の「高齢者世帯等」に障がいのある方が入るか</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>手引きは受領した。福祉サービス13件の対象はいずれも「高齢者世帯等」「65歳以上」「概ね60歳以上」「在宅介護高齢者等」である。①このうち障がいのある方（65歳未満を含む）が対象となる事業はどれか②生活支援ハウスの入居要件と空き状況③緊急通報システム事業の「等」の範囲④障がいのある方の利用実績（令和6・7年度）</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>65歳到達者の移行先を介護保険給付に限ると評価が実態と合わない。住まいの選択肢を比べるためにも「等」の範囲が要る。成年後見制度の助成だけは「障がいや認知症などにより」と障がいのある方が明示されている</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>令和8年10月20日</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>M-51</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>権利擁護・成年後見の件数</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>①権利擁護・成年後見に関する相談件数②会津権利擁護・成年後見センターへの接続件数③申立支援件数④報酬助成件数⑤親亡き後に関する相談件数⑥共同生活援助・単身生活への移行件数。あわせて令和8年度の住民向け成年後見講座の開催実績と村の窓口</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>第6章の評価を利用者数3人だけで書くと、制度に乗る前の相談と助成の実態が見えない</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>令和8年10月20日</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>M-52</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>緊急連絡カードの配布対象と障がい分野での活用</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>様式は受領した（2人分。持病・お薬、かかりつけ医、緊急連絡先、備考、本人の同意欄）。①配布の対象と実績②実施している課と事業名③障がいのある方・医療的ケアが必要な方・ひとり暮らしの方への配布と活用の状況④消防（救急隊）との情報共有の取決めの有無⑤備考欄に障がいの特性や意思疎通の方法を書いている例があるか</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>様式には障がいの特性・意思疎通の方法・医療的ケアの内容を書く欄がないため、備考欄の使い方が要になる。計画に「障がい者へ配布する」と確定で書く前に活用の状況を確かめる必要がある</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>令和8年10月20日</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>M-55</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>高齢者世帯等除雪サービス事業の利用実績</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>直近3年度について、①全利用世帯数②うち障がいのある方がいる世帯数③うち65歳未満の障がい者世帯数</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>実績がないことと対象外であることは別である。利用がある場合は、既存事業への接続として計画に書ける</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>令和8年10月20日</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>M-56</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>高齢者世帯等除雪サービス事業の助成の内容</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>①助成上限②自己負担③利用回数④除雪の範囲（玄関、生活道路、屋根雪等）⑤対象業者⑥申請方法</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>どこまでを助成するかにより、障がいのある方の生活上の支障が埋まるかが決まる。玄関から道路までが対象外であれば、通所・通院の支障は残る</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>令和8年10月20日</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>M-57</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>冬季の除雪の供給の制約</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>①地区ごとに対応できる業者②豪雪時の人手不足③申請しても利用できなかった世帯④冬季のサービスの停止・遅延</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>需要があっても担い手がなければ埋まらない。第5章2（7）の事業所の受入余力の把握と同じ扱いで記録する</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>令和8年10月27日</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>M-58</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>除雪が困難な世帯を既存事業へつなぐ運用</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>相談支援専門員、民生委員児童委員、社会福祉協議会、地域包括支援センター等から、除雪が困難な障がい者世帯を既存事業へつなぐ運用があるか</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>制度があっても、障がい福祉の相談から高齢福祉の事業へつなぐ流れがなければ使われない。3段階の整理の第1段階（既存事業で対象となる場合）で整えるべきものである</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>令和8年10月27日</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>M-53</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>就労の受け皿（職親委託等）</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>①職親委託制度の実績②村内事業所での雇用実績③特別支援学校卒業者の就労先</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>就労選択支援だけでは一般就労への移行の受け皿が書けない</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>令和8年10月27日</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>M-54</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>地域生活支援拠点等の5機能の実績</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>会津北部地域生活支援拠点について、①相談②緊急時の受入れ③体験の機会及び場④専門的人材の確保養成⑤地域の体制づくりの機能ごとの令和6・7年度の実績と検証・検討の実施回数</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>告示 第二 五は5つの機能の確保を求めている。正本は拠点への参画までしか書いておらず、機能別の実績がない</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>令和8年10月27日</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1127,22 +1481,22 @@
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>W-9</t>
+          <t>W-13</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>第3章3 基本施策の目標値（評価の様式）</t>
+          <t>第5章2（14）冬季の地域生活の継続（新しい項）</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>評価を「実施／未実施」の2択にせず、6区分（①障害福祉で実施／②他制度で対応／③圏域で対応／④ニーズなし／⑤ニーズあり・供給不足／⑥把握不足）で書く旨を注記する</t>
+          <t>積雪が通院・通所・買物・サービスの利用に及ぼす影響と、居宅の周りの除雪が地域生活を続ける前提になる世帯があることを書く。村に既存の除雪支援があることを踏まえ、対象の確認→既存事業への接続→必要な場合のみ対象拡大 の3段階で進めると書く。あわせて、冬季に実利用量が減る場合は需要が少ないのではなく供給とアクセスの制約として扱うことを書く</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>再レビュー9</t>
+          <t>再レビュー（除雪支援の整理）。高齢者サービスの手引き</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -1150,39 +1504,71 @@
           <t>追記できる</t>
         </is>
       </c>
-      <c r="F16" s="9" t="inlineStr">
-        <is>
-          <t>原典あり（村の評価シートの様式）</t>
+      <c r="F16" s="12" t="inlineStr">
+        <is>
+          <t>原典あり</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
+          <t>W-9</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>第3章3 基本施策の目標値（評価の様式）</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>評価を「実施／未実施」の2択にせず、6区分（①障害福祉で実施／②他制度で対応／③圏域で対応／④ニーズなし／⑤ニーズあり・供給不足／⑥把握不足）で書く旨を注記する</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>再レビュー9</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>追記できる</t>
+        </is>
+      </c>
+      <c r="F17" s="10" t="inlineStr">
+        <is>
+          <t>原典あり（村の評価シートの様式）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
           <t>W-10</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>第1章6 計画の推進体制</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>年次の点検評価に用いる様式として7列（実績／ニーズ／障害福祉での供給／他制度による代替・補完／圏域利用／未充足／令和9〜11年度の対応）を定める旨を書く</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>再レビューの結論</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>追記できる</t>
         </is>
       </c>
-      <c r="F17" s="10" t="inlineStr">
+      <c r="F18" s="9" t="inlineStr">
         <is>
           <t>原典あり（法第88条の2）</t>
         </is>
@@ -1197,13 +1583,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1495,71 +1881,75 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>W-4</t>
+          <t>W-13</t>
         </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>表の後</t>
+          <t>注記後</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>第5章2（11）災害時の備え（W-8の4場面の表の後）</t>
+          <t>第5章2（14）冬季の地域生活の継続（新しい項として末尾に追加）</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>本村では、本人の身に何か起きたときの備えが場面ごとに分かれています。どの場面にどの仕組みが働くのかを整理したうえで、障が…</t>
+          <t>【村へ確認（M-25）】…</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>再レビュー6。村の緊急連絡カードの様式</t>
+          <t>再レビュー（除雪支援の整理）。令和8年度 北塩原村高齢者サービスの手引き</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>このうち急病時については、村に、住所、氏名、生年月日、持病と常用している薬、かかりつけ医及び緊急連絡先を記入し、本人の同意のうえで電話機や冷蔵庫の近くに備え付けて救急隊に伝える様式があります。この様式には障がいの特性、意思疎通の方法及び医療的ケアの内容を書く欄がないため、備考の欄にこれらを書き加えられるようにすることを検討します。医療的ケアが必要な方、重度の障がいのある方及びひとり暮らしの方について、この様式がどの程度使われているかを確かめたうえで、必要に応じて対象の拡大と周知を図ります。</t>
+          <t>本村は積雪寒冷地であり、冬期間の積雪は通院、通所、買物及び福祉サービスの利用に影響します。単身の世帯や家族介護者が高齢になった世帯では、居宅の周りの除雪そのものが、地域生活を続けるうえでの課題になる場合があります。
+本村には、除雪が困難な高齢者世帯等を対象として居宅の除雪経費の一部を助成する事業が既にあります。このため、障がいのある方の冬季の支援については、新たな事業を設けることから考えるのではなく、まず既存の事業の対象と利用の状況を確かめ、次の順序で進めます。
+［表］段階 ／ 確かめること ／ 確かめた後にすること（3行）
+確かめる事項は、対象要件、利用の実績、助成の内容（助成の上限、自己負担、除雪の範囲）、地区ごとに対応できる業者の有無、及び相談支援専門員や民生委員児童委員から既存の事業につなぐ運用の有無です。豪雪時の孤立、救急の搬送路の確保及び医療的ケアが必要な方の居宅への経路については、（11）の災害時の備え及び村の地域防災計画とあわせて整理します。
+なお、冬季に支援が届かないことは、サービスの必要量が少ないことを意味しません。支給決定を受けていても、冬季に訪問の車両が自宅まで入れないために実際の利用量が減っている場合は、需要が少ないのではなく供給とアクセスの制約として扱い、（７）の事業所の受入余力の把握とあわせて記録します。</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>W-7</t>
+          <t>W-4</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>表の後</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>第5章1（3）居住系サービス（移植11の後）</t>
+          <t>第5章2（11）災害時の備え（W-8の4場面の表の後）</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>なお、国の基本指針は、生活介護、就労継続支援Ｂ型及び施設入所支援の必要な量の見込みについて、継続入所者（計画期間の開始前…</t>
+          <t>本村では、本人の身に何か起きたときの備えが場面ごとに分かれています。どの場面にどの仕組みが働くのかを整理したうえで、障が…</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>再レビュー5。令和8年度 北塩原村高齢者サービスの手引き</t>
+          <t>再レビュー6。村の緊急連絡カードの様式</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>親が亡くなった後の住まいを考えるときには、共同生活援助だけを前提とせず、本人の年齢と必要な支援に応じて選択肢を比べます。本村には、概ね60歳以上で自宅での独立した生活に不安のある方を対象とし、管理人が常駐する一人暮らし高齢者向けの住まい（生活支援ハウス）があります。知的障がい又は精神障がいのある方が60歳代に入り、親が亡くなって独居が難しくなる場合には、共同生活援助とこうした高齢者向けの住まいのどちらが本人に合うかを、介護保険の利用の可否とあわせて個別に検討します。なお、高齢者向けの事業は対象を高齢者世帯等としており、障がいのある方が対象となるかは事業ごとに確認します。</t>
+          <t>このうち急病時については、村に、住所、氏名、生年月日、持病と常用している薬、かかりつけ医及び緊急連絡先を記入し、本人の同意のうえで電話機や冷蔵庫の近くに備え付けて救急隊に伝える様式があります。この様式には障がいの特性、意思疎通の方法及び医療的ケアの内容を書く欄がないため、備考の欄にこれらを書き加えられるようにすることを検討します。医療的ケアが必要な方、重度の障がいのある方及びひとり暮らしの方について、この様式がどの程度使われているかを確かめたうえで、必要に応じて対象の拡大と周知を図ります。</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>W-11</t>
+          <t>W-7</t>
         </is>
       </c>
       <c r="B15" s="10" t="inlineStr">
@@ -1569,52 +1959,84 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>第5章2（4）広域連携によるサービス提供体制の確保</t>
+          <t>第5章1（3）居住系サービス（移植11の後）</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>本村は人口規模が小さく、村内に障がい福祉サービス事業所が少ないことから、多くのサービスを近隣市町村の事業所に依存していま…</t>
+          <t>なお、国の基本指針は、生活介護、就労継続支援Ｂ型及び施設入所支援の必要な量の見込みについて、継続入所者（計画期間の開始前…</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>令和8年度 北塩原村高齢者サービスの手引きのサービス事業者一覧。障害者総合支援法第41条の2（共生型障害福祉サービス）</t>
+          <t>再レビュー5。令和8年度 北塩原村高齢者サービスの手引き</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>本村には障がい福祉サービスの事業所が３カ所しかありませんが、介護保険の事業所は７カ所あります（居宅介護支援、介護予防支援、訪問介護、通所介護２カ所、認知症対応型共同生活介護２カ所）。このうち訪問介護及び通所介護の事業所は、共生型サービスの指定を受けることにより、介護保険の指定を受けたまま障がい福祉サービスを提供できます。共生型サービスの対象となるのは訪問介護、通所介護及び短期入所生活介護であり、村内では訪問介護１カ所と通所介護２カ所がこれに当たります。本計画期間においては、この３カ所に対して、村から共生型サービス又は基準該当サービスの指定を受けることを働きかけます。村内で居宅介護又は生活介護を受けられるようになれば、冬季の通所と送迎の制約が小さくなります。</t>
+          <t>親が亡くなった後の住まいを考えるときには、共同生活援助だけを前提とせず、本人の年齢と必要な支援に応じて選択肢を比べます。本村には、概ね60歳以上で自宅での独立した生活に不安のある方を対象とし、管理人が常駐する一人暮らし高齢者向けの住まい（生活支援ハウス）があります。知的障がい又は精神障がいのある方が60歳代に入り、親が亡くなって独居が難しくなる場合には、共同生活援助とこうした高齢者向けの住まいのどちらが本人に合うかを、介護保険の利用の可否とあわせて個別に検討します。なお、高齢者向けの事業は対象を高齢者世帯等としており、障がいのある方が対象となるかは事業ごとに確認します。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
+          <t>W-11</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>第5章2（4）広域連携によるサービス提供体制の確保</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>本村は人口規模が小さく、村内に障がい福祉サービス事業所が少ないことから、多くのサービスを近隣市町村の事業所に依存していま…</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>令和8年度 北塩原村高齢者サービスの手引きのサービス事業者一覧。障害者総合支援法第41条の2（共生型障害福祉サービス）</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>本村には障がい福祉サービスの事業所が３カ所しかありませんが、介護保険の事業所は７カ所あります（居宅介護支援、介護予防支援、訪問介護、通所介護２カ所、認知症対応型共同生活介護２カ所）。このうち訪問介護及び通所介護の事業所は、共生型サービスの指定を受けることにより、介護保険の指定を受けたまま障がい福祉サービスを提供できます。共生型サービスの対象となるのは訪問介護、通所介護及び短期入所生活介護であり、村内では訪問介護１カ所と通所介護２カ所がこれに当たります。本計画期間においては、この３カ所に対して、村から共生型サービス又は基準該当サービスの指定を受けることを働きかけます。村内で居宅介護又は生活介護を受けられるようになれば、冬季の通所と送迎の制約が小さくなります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
           <t>W-12</t>
         </is>
       </c>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B17" s="10" t="inlineStr">
         <is>
           <t>本文</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>第6章1（3）成年後見制度利用支援事業の利用状況</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>このような状況の中、本村における高齢化の進展や精神障がい者、知的障がい者の人数の推移から、本制度の必要性はますます高まっ…</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>令和8年度 北塩原村高齢者サービスの手引き・令和8年度住民向け成年後見講座</t>
         </is>
       </c>
-      <c r="F16" s="6" t="inlineStr">
+      <c r="F17" s="6" t="inlineStr">
         <is>
           <t>本村の成年後見制度の利用支援は、障がいや認知症などにより自身で決めることに不安のある方を対象とし、申立てに要する経費及び後見人等の報酬を助成するものです（一定の要件があります）。高齢の方だけでなく、障がいのある方も対象です。また令和８年度には、会津圏域の11市町村と会津権利擁護・成年後見センターの共催により、住民向けの成年後見講座を開催しています。本村はその主催者の一員であり、障がいのある方とその家族にも参加を呼びかけます。</t>
         </is>
@@ -1629,7 +2051,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2245,12 +2667,12 @@
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>無料路線バス・コミュニティバス、除雪事業</t>
+          <t>無料路線バス・コミュニティバス、高齢者世帯等除雪サービス事業</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>既存一般施策での代替可否を先に評価</t>
+          <t>既存一般施策での代替可否を先に評価。冬季支援は11シートの6つの評価事項で見る</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
@@ -2487,7 +2909,7 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>防災・BCP・緊急時</t>
+          <t>防災・BCP・緊急時（冬季孤立対策を含む）</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
@@ -2502,7 +2924,7 @@
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>平時〜災害時を段階別に再構成</t>
+          <t>平時〜災害時を段階別に再構成。豪雪時の孤立・救急搬送路の確保・医療的ケアが必要な方の居宅へのアクセスを加える</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
@@ -2633,17 +3055,17 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>圏域で対応</t>
+          <t>圏域・他機関で対応</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>村内に事業所がなく、圏域（会津障がい保健福祉圏域・会津北部4町村）の事業所の利用又は共同整備で確保している</t>
+          <t>村内に事業所がなく、圏域（会津障がい保健福祉圏域・会津北部4町村）の事業所の利用又は共同整備で確保している。社会福祉協議会、民生委員児童委員、地域の組織が担っているものを含む</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>就労継続支援Ｂ型・生活介護・共同生活援助。地域生活支援拠点は会津北部に参画</t>
+          <t>就労継続支援Ｂ型・生活介護・共同生活援助。地域生活支援拠点は会津北部に参画。寝具洗濯・訪問理美容・家族介護継続支援は社会福祉協議会に委託</t>
         </is>
       </c>
     </row>
@@ -2878,22 +3300,22 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>高齢者世帯等除雪サービス事業の障がい者世帯への適用</t>
+          <t>除雪支援</t>
         </is>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>障がい分野での実績なし</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>⑥</t>
+          <t>②＋⑥</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>事業は「除雪が困難な高齢者世帯等」を対象とし、非課税世帯に居宅の除雪経費の一部を助成するもの。「等」に障がいのみを理由とする世帯が含まれるかを確認していない（照会M-49）</t>
+          <t>村には「高齢者世帯等除雪サービス事業」があり（除雪が困難な高齢者世帯等に居宅の除雪経費の一部を助成。非課税世帯）、他の制度で対応している可能性がある。ただし「等」に障がいのみを理由とする世帯が含まれるか、利用の実績があるかを確認していない（照会M-49・M-55〜M-58）。障がい者向けの除雪事業がないとは現時点では断定できない</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -4043,223 +4465,413 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="64" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="54" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>この再レビューで生じた村への照会（M-49〜M-54）</t>
+          <t>除雪支援（新設と決めつけず、既存事業への接続から考える）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>既存の照会はM-48まで。M-50（高齢者福祉施策の対象要件と手引きの提供）は、1枚で65歳移行・住まい・冬季支援・移動の4つに答えが出る。</t>
+          <t>村には「高齢者世帯等除雪サービス事業」があり、除雪が困難な高齢者世帯等に居宅の除雪経費の一部を助成している（非課税世帯）。障がい者向けの除雪事業がないとは現時点では断定できない。</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>番号</t>
+          <t>段階</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>事項</t>
+          <t>どういう場合か</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>聞きたいこと</t>
+          <t>すること</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>なぜ要るか</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>期限の目安</t>
+          <t>補足</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>M-49</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>高齢者世帯等除雪サービス事業の「等」の範囲</t>
+          <t>既存事業で障がい者世帯も対象となる</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>手引きでは「除雪が困難な高齢者世帯等」を対象とし、非課税世帯に居宅の除雪経費の一部を助成するとされている。①「等」に障がいのみを理由とする世帯が含まれるか②障がいのある方が属する世帯の利用実績（令和6・7年度）③助成の上限額と申請の方法</t>
+          <t>新規の事業は設けず、障がい福祉計画から既存事業への接続・周知を強化する</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>対象であれば既存事業の活用として書き、対象外でニーズがあれば対象拡大又は障害福祉での補完を検討する。障がい者向け除雪事業を新設すると直ちに書くのは順序が逆になる</t>
-        </is>
-      </c>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
-          <t>令和8年10月20日</t>
+          <t>障がい福祉の相談（相談支援専門員・保健福祉課）から高齢福祉の担当へつなぐ流れを定める</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>M-50</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>高齢者福祉施策の「高齢者世帯等」に障がいのある方が入るか</t>
+          <t>一部の障がい者世帯のみ対象となる</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>手引きは受領した。福祉サービス13件の対象はいずれも「高齢者世帯等」「65歳以上」「概ね60歳以上」「在宅介護高齢者等」である。①このうち障がいのある方（65歳未満を含む）が対象となる事業はどれか②生活支援ハウスの入居要件と空き状況③緊急通報システム事業の「等」の範囲④障がいのある方の利用実績（令和6・7年度）</t>
+          <t>対象要件の拡大、運用の整理、福祉部門間の連携を検討する</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>65歳到達者の移行先を介護保険給付に限ると評価が実態と合わない。住まいの選択肢を比べるためにも「等」の範囲が要る。成年後見制度の助成だけは「障がいや認知症などにより」と障がいのある方が明示されている</t>
-        </is>
-      </c>
-      <c r="E7" s="10" t="inlineStr">
-        <is>
-          <t>令和8年10月20日</t>
+          <t>どの要件で外れるのか（年齢・世帯構成・所得・除雪困難の判定）を確かめたうえで、高齢福祉の担当と協議する</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>M-51</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>権利擁護・成年後見の件数</t>
+          <t>障がいのみを理由とする世帯が対象外で、かつ未充足ニーズが確認される</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>①権利擁護・成年後見に関する相談件数②会津権利擁護・成年後見センターへの接続件数③申立支援件数④報酬助成件数⑤親亡き後に関する相談件数⑥共同生活援助・単身生活への移行件数。あわせて令和8年度の住民向け成年後見講座の開催実績と村の窓口</t>
+          <t>障がい分野での補完策又は村単独施策の必要性を検討する</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>第6章の評価を利用者数3人だけで書くと、制度に乗る前の相談と助成の実態が見えない</t>
-        </is>
-      </c>
-      <c r="E8" s="9" t="inlineStr">
-        <is>
-          <t>令和8年10月20日</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>M-52</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>緊急連絡カードの配布対象と障がい分野での活用</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>様式は受領した（2人分。持病・お薬、かかりつけ医、緊急連絡先、備考、本人の同意欄）。①配布の対象と実績②実施している課と事業名③障がいのある方・医療的ケアが必要な方・ひとり暮らしの方への配布と活用の状況④消防（救急隊）との情報共有の取決めの有無⑤備考欄に障がいの特性や意思疎通の方法を書いている例があるか</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>様式には障がいの特性・意思疎通の方法・医療的ケアの内容を書く欄がないため、備考欄の使い方が要になる。計画に「障がい者へ配布する」と確定で書く前に活用の状況を確かめる必要がある</t>
-        </is>
-      </c>
-      <c r="E9" s="10" t="inlineStr">
-        <is>
-          <t>令和8年10月20日</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>M-53</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>就労の受け皿（職親委託等）</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>①職親委託制度の実績②村内事業所での雇用実績③特別支援学校卒業者の就労先</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>就労選択支援だけでは一般就労への移行の受け皿が書けない</t>
-        </is>
-      </c>
-      <c r="E10" s="9" t="inlineStr">
-        <is>
-          <t>令和8年10月27日</t>
+          <t>この段階に至って初めて新設を検討する。地域生活支援事業の任意事業として組む方法もある</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>確かめる事項</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>照会</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>手引きの記載</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>M-54</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>地域生活支援拠点等の5機能の実績</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>会津北部地域生活支援拠点について、①相談②緊急時の受入れ③体験の機会及び場④専門的人材の確保養成⑤地域の体制づくりの機能ごとの令和6・7年度の実績と検証・検討の実施回数</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>告示 第二 五は5つの機能の確保を求めている。正本は拠点への参画までしか書いておらず、機能別の実績がない</t>
-        </is>
-      </c>
-      <c r="E11" s="10" t="inlineStr">
-        <is>
-          <t>令和8年10月27日</t>
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>対象要件</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>「高齢者世帯等」の「等」に障がい者世帯が含まれるか。障がいのみを理由とする世帯が対象となる条件。身体・知的・精神・難病等の区分ごとの可否、年齢要件、所得要件</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>M-49</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>手引きには「除雪が困難な高齢者世帯等」「非課税世帯」とある</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>利用実績</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>直近3年度の全利用世帯数、うち障がいのある方がいる世帯数、うち65歳未満の障がい者世帯数</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>M-55</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>手引きに記載なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>助成の内容</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>助成上限、自己負担、利用回数、除雪の範囲（玄関、生活道路、屋根雪等）、対象業者、申請方法</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>M-56</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>手引きは「居宅の除雪経費の一部を助成」とのみ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>供給の制約</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>地区ごとに対応できる業者、豪雪時の人手不足、申請しても利用できなかった世帯、冬季のサービスの停止・遅延</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>M-57</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>手引きに記載なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>つなぐ運用</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>相談支援専門員、民生委員児童委員、社会福祉協議会、地域包括支援センター等から、除雪が困難な障がい者世帯を既存事業へつなぐ運用があるか</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>M-58</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>手引きに記載なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>接続する重点施策</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>評価する事項</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>扱い</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>No.6 移動・冬季支援</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>冬季の通院・通所・買物への支障／玄関から道路までの除雪困難／家族による除雪支援の有無／既存除雪事業の利用可否／公共交通・事業所送迎との接続／冬季にサービス利用が中断するケースの有無</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>6つの評価事項として評価シートに置く</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>No.10 地域生活継続・親亡き後・権利擁護</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>単身の障がいのある方／高齢の親と同居する障がいのある方／親亡き後に単身生活へ移行する方／身体機能上除雪が困難な方</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>除雪が地域生活を続ける前提条件になる世帯を、住まいの支援と一体で確認する</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>No.12 防災・BCP・冬季孤立対策</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>豪雪時の孤立／救急搬送路の確保／医療的ケアが必要な方の居宅へのアクセス／停電・燃料不足／緊急時の玄関・避難経路の確保</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>日常の生活支援としての除雪を超える部分は防災施策と接続する</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>誤りやすい整理</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>なぜ誤りか</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>本書での扱い</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>「障がい者向け除雪制度がない」</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>現時点では断定できない。既存の高齢者世帯等除雪サービス事業の対象範囲の確認が先</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>本書は「障がい分野での実績なし」とだけ書き、制度の有無は照会M-49の回答後に判定する</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>「利用実績0＝ニーズなし」</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>制度の対象外、制度が知られていない、担い手の不足の可能性があるため、個別の確認が要る</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>評価は②他制度で対応の可能性あり＋⑥把握不足とする</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>「除雪は防災だけの問題」</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>日常生活、通院、サービスの利用、親亡き後、単身生活、在宅の医療・福祉サービスの継続にも関係する</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>No.6・No.10・No.12の3つに接続する</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>「高齢者施策と障がい施策を別々に新設する」</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>小規模自治体では制度の重複を避け、既存制度の対象拡大・横断利用・相談窓口の連携を先に検討する方が合理的</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>3段階の順序（既存で対象／一部のみ／対象外かつ未充足）で整理する</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t>※ 除雪支援そのものは障がい福祉サービスの給付見込量とは別に扱う。ただし除雪が困難なために次のサービスの利用が妨げられている場合は、需要が少ないのではなく供給とアクセスの制約として評価する： 居宅介護、重度訪問介護、訪問看護等、生活介護、就労系サービス、放課後等デイサービス、短期入所、相談支援、医療機関への通院。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/北塩原村_12重点施策_評価設計.xlsx
+++ b/output/北塩原村_12重点施策_評価設計.xlsx
@@ -1964,7 +1964,7 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>なお、国の基本指針は、生活介護、就労継続支援Ｂ型及び施設入所支援の必要な量の見込みについて、継続入所者（計画期間の開始前…</t>
+          <t>ここでいう継続入所者とは、…</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">

--- a/output/北塩原村_12重点施策_評価設計.xlsx
+++ b/output/北塩原村_12重点施策_評価設計.xlsx
@@ -707,7 +707,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>村内の介護保険の事業所は7カ所ある（居宅介護支援、介護予防支援、訪問介護、通所介護2カ所、認知症対応型共同生活介護2カ所）。このうち訪問介護1カ所と通所介護2カ所は共生型サービスの指定を受けられるため、働きかけの相手が具体的に分かった。障がい福祉の事業所が村内に3カ所しかない本村では、確保のための方策の中心になりうる</t>
+          <t>村内の介護保険の事業所は7カ所ある（居宅介護支援、介護予防支援、訪問介護、通所介護2カ所、認知症対応型共同生活介護2カ所）。このうち訪問介護1カ所と通所介護2カ所は共生型サービスの対象となるサービスの種類であり、検討の相手が具体的に分かった。ただし共生型は指定の手続の特例であって、事業者の申請と基準を満たすことが要る。村内の障がい福祉の事業所は3カ所であり、介護保険の資源を障がい福祉の供給に生かせるかは確保のための方策の論点になる</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>村内の介護保険の事業所7カ所（居宅介護支援、介護予防支援、訪問介護、通所介護2カ所、認知症対応型共同生活介護2カ所）を示し、うち訪問介護1カ所と通所介護2カ所は共生型サービスの指定により障がい福祉サービスを提供できることから、働きかけの相手が具体的に分かることを書く</t>
+          <t>村内の介護保険の事業所7カ所（居宅介護支援、介護予防支援、訪問介護、通所介護2カ所、認知症対応型共同生活介護2カ所）を示し、うち訪問介護1カ所と通所介護2カ所は共生型サービスの対象となるサービスの種類であることから、検討の相手が具体的に分かることを書く。共生型は指定の手続の特例であり、事業者の申請と基準を満たすことが要るため、「指定を受けられる」とは書かない</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -2006,7 +2006,11 @@
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>本村には障がい福祉サービスの事業所が３カ所しかありませんが、介護保険の事業所は７カ所あります（居宅介護支援、介護予防支援、訪問介護、通所介護２カ所、認知症対応型共同生活介護２カ所）。このうち訪問介護及び通所介護の事業所は、共生型サービスの指定を受けることにより、介護保険の指定を受けたまま障がい福祉サービスを提供できます。共生型サービスの対象となるのは訪問介護、通所介護及び短期入所生活介護であり、村内では訪問介護１カ所と通所介護２カ所がこれに当たります。本計画期間においては、この３カ所に対して、村から共生型サービス又は基準該当サービスの指定を受けることを働きかけます。村内で居宅介護又は生活介護を受けられるようになれば、冬季の通所と送迎の制約が小さくなります。</t>
+          <t>本村には障がい福祉サービスの事業所が３カ所（居宅介護、重度訪問介護及び生活介護が各１カ所）あります。これに対して介護保険の事業所は７カ所あります（居宅介護支援、介護予防支援、訪問介護、通所介護２カ所、認知症対応型共同生活介護２カ所）。村内の介護保険の事業所の力を障がい福祉の供給に生かせないかを考えます。
+共生型サービスは、新しいサービスの種類ではありません。介護保険と障がい福祉のどちらかの指定を受けている事業所が、もう一方の指定も受けやすくするための指定の手続の特例です。指定は「共生型通所介護」のような別の名前ではなく、従来どおり「通所介護」「生活介護」等として行われます。自動的に指定されるものではなく、事業所からの申請が必要です。既に出した書類の記載を省略できる点が簡素化されています。
+共生型の対象となるのは、訪問介護と居宅介護・重度訪問介護、通所介護・地域密着型通所介護と生活介護・自立訓練・児童発達支援・放課後等デイサービス、通所リハビリテーションと自立訓練（機能訓練）、短期入所生活介護と短期入所、及び小規模多機能型居宅介護等の通いと泊まりです。村内には訪問介護１カ所と通所介護２カ所があり、短期入所生活介護の事業所はありません。したがって短期入所については、村内の共生型ではなく圏域での確保として扱います。
+進め方は次のとおりです。まず、村内の障がい福祉サービスの３カ所と介護保険の訪問介護・通所介護の事業所について、どの指定の形で提供しているか（通常の指定か、共生型の指定か、基準該当障害福祉サービスとしての取扱いか）を確かめます。そのうえで、障がい福祉のサービスを行っていない事業所について、村内の需要、受入れの余力、職員の体制、設備、障がいの特性への対応力を確かめ、必要が認められる場合に、共生型の指定、通常の指定又は基準該当障害福祉サービスとしての取扱いのうちどれが適しているかを事業者と検討します。なお、基準該当障害福祉サービスは指定を受ける制度ではなく、通常の基準の一部を満たさない場合でも村が給付の対象として取り扱う仕組みです。
+数を増やすことが目的ではありません。介護保険と障がい福祉では、通所の例でいえば、定員（障がい福祉は原則20人以上、介護保険は定めなし）、職員の配置（障がい福祉は平均障害支援区分に応じ、介護保険は一律）、設備（障がい福祉は訓練・作業室、介護保険は食堂及び機能訓練室で利用者１人あたり３平方メートル）という違いがあります。一方の指定を受けていることは、もう一方の基準を満たしていることを意味しません。本計画が成果とするのは、65歳に達しても支援が途切れないこと、冬季を含めて実際に通えること、障がいの特性に応じた支援の質が保たれることです。</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3734,6 +3738,28 @@
       <c r="D11" s="5" t="inlineStr">
         <is>
           <t>当方の補足</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>同じ事業所で続けられたか</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>65歳の前後で事業所が変わったか。変わらなかった場合、その事業所がどの指定の形で提供しているか（通常の指定・共生型の指定・基準該当障害福祉サービスとしての取扱い）</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>国が共生型サービスを設けたねらいの一つは、65歳以上になっても使い慣れた事業所でサービスを利用しやすくすることである。中断がなくても事業所と職員が変わっていれば、本人にとっては大きい変化である。事業所数ではなく継続できた人数で評価する</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>原典あり（共生型サービスの概要000897169・正本 第5章5（2）ＫＹ-1）／村内の事業所の指定の形は照会Ｍ-106</t>
         </is>
       </c>
     </row>

--- a/output/北塩原村_12重点施策_評価設計.xlsx
+++ b/output/北塩原村_12重点施策_評価設計.xlsx
@@ -678,7 +678,7 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>08bシート。照会M-49・M-55〜M-58</t>
+          <t>08bシート。照会Ｍ-49・Ｍ-55〜Ｍ-58</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>10件（M-49〜M-58）。M-50（高齢者福祉施策の対象要件と手引きの提供）が最も効く。1枚で65歳移行・住まい・冬季支援・移動の4つに答えが出る</t>
+          <t>10件（Ｍ-49〜M-58）。Ｍ-50（高齢者福祉施策の対象要件と手引きの提供）が最も効く。1枚で65歳移行・住まい・冬季支援・移動の4つに答えが出る</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -778,14 +778,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>この再レビューで生じた村への照会（M-49〜M-58）</t>
+          <t>この再レビューで生じた村への照会（Ｍ-49〜M-58）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>既存の照会はM-48まで。M-50（高齢者福祉施策の対象要件と手引きの提供）は、1枚で65歳移行・住まい・冬季支援・移動の4つに答えが出る。</t>
+          <t>既存の照会はＭ-48まで。Ｍ-50（高齢者福祉施策の対象要件と手引きの提供）は、1枚で65歳移行・住まい・冬季支援・移動の4つに答えが出る。</t>
         </is>
       </c>
     </row>
@@ -819,7 +819,7 @@
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>M-49</t>
+          <t>Ｍ-49</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -846,7 +846,7 @@
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>M-50</t>
+          <t>Ｍ-50</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -873,7 +873,7 @@
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>M-51</t>
+          <t>Ｍ-51</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -900,7 +900,7 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>M-52</t>
+          <t>Ｍ-52</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -927,7 +927,7 @@
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>M-55</t>
+          <t>Ｍ-55</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -954,7 +954,7 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>M-56</t>
+          <t>Ｍ-56</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -981,7 +981,7 @@
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>M-57</t>
+          <t>Ｍ-57</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -1008,7 +1008,7 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>M-58</t>
+          <t>Ｍ-58</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -1035,7 +1035,7 @@
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>M-53</t>
+          <t>Ｍ-53</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
@@ -1062,7 +1062,7 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>M-54</t>
+          <t>Ｍ-54</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>追記できる（制度の考え方として書く。個別の事業の対象要件は照会M-50の回答後）</t>
+          <t>追記できる（制度の考え方として書く。個別の事業の対象要件は照会Ｍ-50の回答後）</t>
         </is>
       </c>
       <c r="F6" s="9" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>照会M-53の回答後（村に職親委託の実績があるかを確認）</t>
+          <t>照会Ｍ-53の回答後（村に職親委託の実績があるかを確認）</t>
         </is>
       </c>
       <c r="F10" s="9" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>枠組みは追記できる（件数は照会M-51の回答後）</t>
+          <t>枠組みは追記できる（件数は照会Ｍ-51の回答後）</t>
         </is>
       </c>
       <c r="F11" s="10" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>枠組みは追記できる（配布対象と活用状況は照会M-52の回答後）</t>
+          <t>枠組みは追記できる（配布対象と活用状況は照会Ｍ-52の回答後）</t>
         </is>
       </c>
       <c r="F15" s="10" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（M-25）】…</t>
+          <t>【村へ確認（Ｍ-25）】…</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>原典で確認。2人分の様式であり高齢者の夫婦世帯を想定した作り。障がいの特性、意思疎通の方法、医療的ケアの内容を書く欄はなく、備考欄に頼ることになる。発行者名・配布対象・配布実績はカードに記載がないため照会M-52は引き続き要る</t>
+          <t>原典で確認。2人分の様式であり高齢者の夫婦世帯を想定した作り。障がいの特性、意思疎通の方法、医療的ケアの内容を書く欄はなく、備考欄に頼ることになる。発行者名・配布対象・配布実績はカードに記載がないため照会Ｍ-52は引き続き要る</t>
         </is>
       </c>
     </row>
@@ -2175,7 +2175,7 @@
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>※ 別の原典で裏づけが取れているもの：村民向け路線バスICカード事業の創設年度（アンケート調査.pdf 資料3）、移動支援の対象事業所の把握不足（意見・提案.pdf No.5）、会津権利擁護・成年後見センターの設置と成年後見制度利用支援事業の利用状況（正本 第6章）。なお職親委託制度は3資料に記載がなく、照会M-53のままである。</t>
+          <t>※ 別の原典で裏づけが取れているもの：村民向け路線バスICカード事業の創設年度（アンケート調査.pdf 資料3）、移動支援の対象事業所の把握不足（意見・提案.pdf No.5）、会津権利擁護・成年後見センターの設置と成年後見制度利用支援事業の利用状況（正本 第6章）。なお職親委託制度は3資料に記載がなく、照会Ｍ-53のままである。</t>
         </is>
       </c>
     </row>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>年齢ごとの移行の表（6歳・15〜17歳・18歳・18〜22歳・20歳・40歳・65歳）は正本に入れた。台帳そのものは村の移行管理台帳（M-18）待ち</t>
+          <t>年齢ごとの移行の表（6歳・15〜17歳・18歳・18〜22歳・20歳・40歳・65歳）は正本に入れた。台帳そのものは村の移行管理台帳（Ｍ-18）待ち</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
@@ -2602,7 +2602,7 @@
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>確認する6事項（卒業予定者数と卒業年度・進路希望・就労選択支援の利用予定・放課後等デイサービスの終了・送迎と冬季の通所可否・医療的ケアと強度行動障害の有無）は正本に入れた。名簿は村の照会（M-21）待ち</t>
+          <t>確認する6事項（卒業予定者数と卒業年度・進路希望・就労選択支援の利用予定・放課後等デイサービスの終了・送迎と冬季の通所可否・医療的ケアと強度行動障害の有無）は正本に入れた。名簿は村の照会（Ｍ-21）待ち</t>
         </is>
       </c>
       <c r="H16" s="7" t="inlineStr">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>医療的ケア児等コーディネーターと協議の場は正本にある。救急医療情報（持病・常用薬・かかりつけ医）との接続はW-4として正本に入れた。村資料にある「医療的ケアサポート会議」との関係は照会M-41</t>
+          <t>医療的ケア児等コーディネーターと協議の場は正本にある。救急医療情報（持病・常用薬・かかりつけ医）との接続はW-4として正本に入れた。村資料にある「医療的ケアサポート会議」との関係は照会Ｍ-41</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr">
@@ -3238,7 +3238,7 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>対象は要支援者名簿登載者28名。担当課や関係機関の連携不足により策定が遅れている。村資料どうしで件数が食い違う（照会M-42）</t>
+          <t>対象は要支援者名簿登載者28名。担当課や関係機関の連携不足により策定が遅れている。村資料どうしで件数が食い違う（照会Ｍ-42）</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -3319,7 +3319,7 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>村には「高齢者世帯等除雪サービス事業」があり（除雪が困難な高齢者世帯等に居宅の除雪経費の一部を助成。非課税世帯）、他の制度で対応している可能性がある。ただし「等」に障がいのみを理由とする世帯が含まれるか、利用の実績があるかを確認していない（照会M-49・M-55〜M-58）。障がい者向けの除雪事業がないとは現時点では断定できない</t>
+          <t>村には「高齢者世帯等除雪サービス事業」があり（除雪が困難な高齢者世帯等に居宅の除雪経費の一部を助成。非課税世帯）、他の制度で対応している可能性がある。ただし「等」に障がいのみを理由とする世帯が含まれるか、利用の実績があるかを確認していない（照会Ｍ-49・Ｍ-55〜Ｍ-58）。障がい者向けの除雪事業がないとは現時点では断定できない</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>村の給付実績（M-19で系列を確定）</t>
+          <t>村の給付実績（Ｍ-19で系列を確定）</t>
         </is>
       </c>
     </row>
@@ -3428,7 +3428,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>アンケート、相談記録、移行管理台帳（M-18）</t>
+          <t>アンケート、相談記録、移行管理台帳（Ｍ-18）</t>
         </is>
       </c>
     </row>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>高齢者サービスの手引き（原典未入手。照会M-49〜M-51）</t>
+          <t>高齢者サービスの手引き（原典未入手。照会Ｍ-49〜Ｍ-51）</t>
         </is>
       </c>
     </row>
@@ -3693,7 +3693,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>原典あり（高齢者サービスの手引き）／障がいのある方が対象となるかは照会M-50</t>
+          <t>原典あり（高齢者サービスの手引き）／障がいのある方が対象となるかは照会Ｍ-50</t>
         </is>
       </c>
     </row>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>圏域で移動支援を実施している事業所の有無を確認する（照会M-46）</t>
+          <t>圏域で移動支援を実施している事業所の有無を確認する（照会Ｍ-46）</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>照会M-51</t>
+          <t>照会Ｍ-51</t>
         </is>
       </c>
     </row>
@@ -4190,7 +4190,7 @@
       </c>
       <c r="E11" s="10" t="inlineStr">
         <is>
-          <t>照会M-51</t>
+          <t>照会Ｍ-51</t>
         </is>
       </c>
     </row>
@@ -4217,7 +4217,7 @@
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>照会M-51</t>
+          <t>照会Ｍ-51</t>
         </is>
       </c>
     </row>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="E13" s="10" t="inlineStr">
         <is>
-          <t>照会M-51</t>
+          <t>照会Ｍ-51</t>
         </is>
       </c>
     </row>
@@ -4271,7 +4271,7 @@
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>照会M-51</t>
+          <t>照会Ｍ-51</t>
         </is>
       </c>
     </row>
@@ -4298,7 +4298,7 @@
       </c>
       <c r="E15" s="10" t="inlineStr">
         <is>
-          <t>照会M-51・M-50</t>
+          <t>照会Ｍ-51・Ｍ-50</t>
         </is>
       </c>
     </row>
@@ -4637,7 +4637,7 @@
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>M-49</t>
+          <t>Ｍ-49</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -4659,7 +4659,7 @@
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>M-55</t>
+          <t>Ｍ-55</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>M-56</t>
+          <t>Ｍ-56</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>M-57</t>
+          <t>Ｍ-57</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>M-58</t>
+          <t>Ｍ-58</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>本書は「障がい分野での実績なし」とだけ書き、制度の有無は照会M-49の回答後に判定する</t>
+          <t>本書は「障がい分野での実績なし」とだけ書き、制度の有無は照会Ｍ-49の回答後に判定する</t>
         </is>
       </c>
     </row>

--- a/output/北塩原村_12重点施策_評価設計.xlsx
+++ b/output/北塩原村_12重点施策_評価設計.xlsx
@@ -1067,12 +1067,12 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>地域生活支援拠点等の5機能の実績</t>
+          <t>地域生活支援拠点等の5機能の令和6・7年度の実績</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>会津北部地域生活支援拠点について、①相談②緊急時の受入れ③体験の機会及び場④専門的人材の確保養成⑤地域の体制づくりの機能ごとの令和6・7年度の実績と検証・検討の実施回数</t>
+          <t>会津北部地域生活支援拠点について、①相談②緊急時の受入れ③体験の機会及び場④専門的人材の確保養成⑤地域の体制づくりの機能ごとの令和6・7年度の実績と検証・検討の実施回数。整備の年度（令和3年度）、コーディネーター業務の委託先（地域生活支援センターいなわしろ）及び検証・検討回数の基準（令和4年度末0回/年）は第4次北塩原村障がい者計画が記しているため、重ねてお尋ねしない</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
